--- a/光伏配储项目/电价数据/2026/富远站.xlsx
+++ b/光伏配储项目/电价数据/2026/富远站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.42948</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.78818</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.47605</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.49716</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.4357</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.44283</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.38939</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.3715</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.36644</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.35764</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.36148</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.35782</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36401</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.3856</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.38225</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.3993</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.419</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.36285</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31088</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.35093</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.24312</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.1335</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>-0.00594</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.07490999999999999</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.07870999999999999</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.06428</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5135700000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.55855</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.74193</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.14479</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39627</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.37256</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43383</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44061</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6674</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.8910399999999999</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.50099</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.21573</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.34877</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.17556</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.03656</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.31049</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.41194</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45518</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.70678</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7584099999999999</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.12692</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95138</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.91053</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8072999999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.7696000000000001</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51927</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.49012</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47016</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.42093</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43123</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7319500000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.90813</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.97246</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.51307</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5416299999999999</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.52038</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.52052</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.50183</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40767</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.48236</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38416</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.39243</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.51432</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.40257</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.38859</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.48017</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.43466</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.43423</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.42954</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.51005</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.60982</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.50747</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.48573</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.55048</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.5685</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38553</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.36799</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.40077</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49567</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.26094</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04743</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.17803</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.04663</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.42641</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.40652</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.5684199999999999</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.18742</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.01717</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>-0.01333</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.31804</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.604</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.76986</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.80047</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.18977</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.40664</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.14227</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.86294</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.22979</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.12656</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.24189</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.99754</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.11084</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.66965</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.00424</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.92826</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.9815700000000001</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.81811</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.56531</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.4912</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45504</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.46637</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.49936</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45464</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43276</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.44868</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3341</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35741</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33546</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5221399999999999</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.50103</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.50041</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37292</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45222</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.42089</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.37413</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39551</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38913</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43839</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45553</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3379</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37548</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.4039</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3727</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37319</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36621</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.3558</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.40342</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.37857</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.4013</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.40714</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.48677</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44823</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.40054</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.22543</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.36556</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.79963</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.02339</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.4459</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43467</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.36803</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.45193</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.09842000000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.12462</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.32559</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62919</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.66796</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46992</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5074</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.16283</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.20341</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.04805</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.29095</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.10102</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>-0.04305</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43748</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50726</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.62999</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.21376</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5250499999999999</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.48548</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.40627</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.1318</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.4372200000000001</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.46195</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39998</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34298</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52391</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.51085</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44532</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39726</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39616</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.40041</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3642</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39655</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39397</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45928</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36657</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36355</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.36507</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33552</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.34144</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35515</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.39261</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.3816000000000001</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34707</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39842</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42213</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.43676</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.41684</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34205</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.30509</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.5956</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.31553</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.21668</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.18945</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.29859</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.34558</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.30732</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.40824</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6425700000000001</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30161</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.21515</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.4119</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.20684</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.44639</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.47632</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.52754</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45112</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.47481</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40432</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.45665</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.39478</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43826</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.56062</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.5238200000000001</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.49571</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.5045500000000001</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.44797</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.42542</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.41718</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.35598</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34491</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.33136</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37978</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35777</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31759</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31671</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31547</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30902</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30846</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30606</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.30502</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28575</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30503</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29974</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27092</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.25969</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.05867</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13274</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.03796</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.04597</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.04785</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2341</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29636</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.36528</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.37461</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.38065</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.44941</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.36212</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.37444</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45206</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34649</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.3537</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34344</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.32883</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37565</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.43794</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.31226</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.24005</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.21556</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.28549</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.07909999999999999</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.32753</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.2241</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.27636</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.25628</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.23729</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.28879</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.22512</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.3156600000000001</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.27999</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.2498</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.28394</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10152</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.0428</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29314</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00577</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19812</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04523</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26348</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.14073</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.01095</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.05226</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05044</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.32253</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.33479</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31975</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.3814</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43064</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.46053</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39838</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78573</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88747</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.86972</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.61305</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.55591</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42033</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39524</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35744</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.39685</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.41043</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37987</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.33551</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4461</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.5012099999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.36047</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.57055</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.65583</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8913099999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47642</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.48818</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.40819</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.7121799999999999</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.44471</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85746</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.33393</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.36111</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.47136</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.2966</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.48392</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.60103</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.40997</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3476</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31899</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.29541</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3076</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29685</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30125</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30768</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.22604</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.27879</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.28026</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.29243</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.28273</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.3206</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.30766</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.31934</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.33381</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.89574</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.40034</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.35187</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.34687</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.32543</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.31323</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.31592</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.31716</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.32252</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.32076</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.33418</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.31661</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.3219</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.3117200000000001</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.10218</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.26062</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>-0.04064</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.31046</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.2546</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.27275</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.14353</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.26149</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.25997</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20403</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29164</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.26562</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31285</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.31981</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29646</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.26381</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.30789</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.28531</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.3217</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.31876</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.32801</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33638</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.43586</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.4462</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.37568</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.41117</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.27884</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8844099999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.4846</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.20482</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7121000000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80588</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.66198</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.31207</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45055</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50274</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.39532</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41323</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.38205</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.39146</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40377</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42791</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.4263</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.34979</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40362</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.33095</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.48572</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.23581</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28772</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31797</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29536</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.47014</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.04236</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25533</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.14807</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27329</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27739</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.02953</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34256</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.2691</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.26537</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.31393</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28769</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2917</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.29523</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28991</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30899</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32372</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34105</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35309</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.33635</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.49344</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.67708</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.40546</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30824</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.29908</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.28543</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.28835</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.22638</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.31512</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.23723</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.23565</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.23303</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.23229</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.2135</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.26278</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.28287</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.30543</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.21692</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.21625</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.30087</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.29679</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.07984000000000001</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.24028</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.25724</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.08034999999999999</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.26015</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.27129</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.24985</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29511</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.22136</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.31719</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.21036</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.22238</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.11089</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.11679</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>-0.02221</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28671</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>-0.00677</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>-0.01861</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.27173</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.02029</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.20129</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>-0.01536</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25787</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.27842</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>-0.01495</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>-0.04042</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.01296</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>-0.04152</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.10871</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29194</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.30357</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.31417</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.31778</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.33211</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.42362</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.38727</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.37481</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.37996</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.28313</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.30456</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.39003</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.36863</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3356</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33346</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.31243</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.31763</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35283</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30619</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28759</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28821</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.23668</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.25892</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.18506</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.14387</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.2939</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.18044</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.09612000000000001</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.21696</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30085</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30083</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31502</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.29336</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31288</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.28746</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.24367</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.28204</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.24741</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>-0.01434</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.28929</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32759</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.32137</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.35549</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.35794</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.33692</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.3744</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.41247</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.26947</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.35374</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.37677</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.34333</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.31964</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33387</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32401</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.35073</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.38387</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.31586</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.30881</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.31394</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.30865</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31997</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.32001</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33437</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.32042</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.42165</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.11889</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41555</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.66503</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.36074</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.49731</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.46809</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.35351</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.42601</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46571</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.5037900000000001</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.26752</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.26966</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.19989</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.20411</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.58951</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.37218</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34841</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.36162</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.32519</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.48151</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.37571</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.2932</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.3747799999999999</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.37348</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.3637</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.42091</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.33489</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.5902000000000001</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.47986</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.39359</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.47056</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.45178</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.72068</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38965</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.78324</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.70185</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.67115</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.38624</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.52159</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26619</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.39703</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33608</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.34927</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.40581</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.34946</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.31635</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38977</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.30563</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.2971</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.30275</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.30942</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.24767</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.23235</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.29267</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.2929</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.29338</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.23623</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.30504</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.23822</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.21266</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.26443</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.23796</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.24328</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.25297</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.22964</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.21865</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.26228</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.26892</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.36173</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32809</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32214</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.34543</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.34107</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.35558</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.34818</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.34519</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.25597</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.34475</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.35352</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.37544</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.36662</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.36284</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35852</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.38174</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.37487</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36904</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.38494</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35298</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.36854</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.36596</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34675</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34634</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33427</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34701</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34287</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.34263</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33667</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.33352</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34204</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34273</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33294</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32221</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33077</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32699</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32585</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32688</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37046</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.33398</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34236</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35045</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.35688</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34881</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.3554</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34534</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3761</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.37873</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.41776</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.42093</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.65165</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.83141</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.4396</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.45432</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33896</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37306</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35597</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.3588</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35488</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34961</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35676</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35289</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35413</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35658</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35329</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35685</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.37148</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35334</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35325</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34796</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35468</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.37994</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.35039</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.25117</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.03911</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28195</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.14066</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.00779</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.27563</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.29433</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.20702</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.05497999999999999</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.15555</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.21638</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.20325</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.2726</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.2515</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.2903</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.3762200000000001</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.26304</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.26251</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.34175</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.35911</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35478</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40006</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34142</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.37949</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.41586</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.46296</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.65319</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.6109199999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6422</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.81711</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.54987</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.49751</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40951</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34317</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.37639</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.3405</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.35535</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.33018</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.38478</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.46744</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.37504</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.34028</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.35938</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.43624</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.37013</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.39751</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.41707</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.4536</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.47109</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.53483</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.41493</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.33773</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.33549</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.15098</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.4045</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.35264</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.40632</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.65747</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.7182500000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.08904000000000001</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.10481</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.27193</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3410899999999999</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.17205</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.20489</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.21122</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.17394</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.22433</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.15622</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.2422</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.36396</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.38522</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.40486</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.45482</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.49961</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.59678</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.45265</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.50625</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.45645</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.5141</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.74837</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6024299999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6527000000000001</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.36951</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.36894</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.40534</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.36562</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.41477</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.40471</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.36042</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.33015</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.12786</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.31007</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35984</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35983</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.16067</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37988</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.34044</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32962</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.12653</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.13113</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.16098</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.2814700000000001</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.2894</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>-0.02634</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.14028</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37433</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.36372</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40189</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.28125</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.41275</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.43282</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.26207</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.1225</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>-0.03771</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.03929</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.20796</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32977</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.31603</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.28031</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.42016</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39781</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.38838</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.28846</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.28789</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.30911</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.28693</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.35868</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25651</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.24609</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.26985</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.2593</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.27411</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.23953</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.37454</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.27538</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.22985</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.12773</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.29467</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.11897</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.11812</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.22995</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.11192</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.25021</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.22888</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.11238</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.21648</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.22243</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.24547</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.21928</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.22278</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.22628</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.10872</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.22977</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.10825</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.09176000000000001</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.2438</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.22854</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.20598</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.08273999999999999</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.16509</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.12079</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.14071</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.10397</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.02008</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.1283</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.07131</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.08143</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.12928</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.24707</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.05588</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.01522</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29294</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.25568</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.04366</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>-0.02128</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.27544</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.28613</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.28294</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.02673</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.16468</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.08585</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.05108</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.08269</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.09132</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.10909</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.1567</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.29989</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.32409</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.28735</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.31978</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.30975</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.27262</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.29963</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.27475</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.27528</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.3033</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.28471</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.29152</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.24361</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.25253</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.28749</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.22963</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30289</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.23111</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.27784</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.25996</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.29461</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.2947</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.13967</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.23126</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.22766</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.28429</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.09848</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.23944</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.25447</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.24808</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.12805</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.09182999999999999</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.10077</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.10076</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.09909</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.09909</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.10009</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.23453</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.08993999999999999</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.09909</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.09925</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.22268</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.09190000000000001</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.09181</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.10502</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.06718</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.25619</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.10956</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.00154</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.0008900000000000001</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1559</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02273</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01432</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04102</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04863</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02947</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.0381</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00261</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.28017</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04929</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03563</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01166</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03529</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20787</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29407</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28179</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.29509</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.10298</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30334</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.32521</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3041</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.32698</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.3679</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.30233</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.5288200000000001</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.48744</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.34434</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.20096</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.35702</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.35711</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.24699</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.23218</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.23894</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.2359</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.11215</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.22889</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.21487</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.11836</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.07216</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.09056</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.10005</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.11374</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.07856999999999999</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.12661</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.13371</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.14446</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.42707</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.26884</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.10025</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.26168</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.55238</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8722300000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8719199999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.03716</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.1641</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04851</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.00262</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>-0.04916</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30593</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.04435</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25442</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32008</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.35573</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32807</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.34639</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.35732</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.05342</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.6484500000000001</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.5430199999999999</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.5825399999999999</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.0484</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.96024</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.55336</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.71345</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.60012</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.82262</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.82087</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.82499</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.9214199999999999</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.54222</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.59605</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.55008</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35888</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.33239</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.39222</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.45941</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.23223</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.43079</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.47993</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.36776</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.26429</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.29195</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.26125</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.25482</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.2488</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.22566</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.22866</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.10465</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.239</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.2518</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.29051</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.30895</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.2845299999999999</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.30102</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.17337</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.36574</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.06558</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.11611</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>-0.04901</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.10152</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.25036</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.28404</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.29999</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.29049</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25985</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30353</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32576</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31561</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31438</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32608</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32677</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3486</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.39179</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.37092</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.3436</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.41089</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.38878</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.5159600000000001</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.35439</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.39826</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.33315</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.31441</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.39274</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.39033</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.36233</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.35404</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.33264</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.33016</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.3247</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.33662</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.44458</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.67999</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.425</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.44409</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.37645</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37316</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34069</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29965</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32265</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.31249</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32204</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33804</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42095</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.40374</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.4099</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.24995</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8036799999999999</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.5796699999999999</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40108</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.41522</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.53025</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.5371699999999999</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.82984</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.61807</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.46205</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.33394</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.35608</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.34539</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.21745</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.32551</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.33427</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.4256</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.35948</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.35138</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.33533</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.33257</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.31488</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3119</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33069</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.33932</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.33024</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33376</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37053</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.35487</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34517</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.31009</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3497</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34411</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.35389</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.36406</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.40768</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39708</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.45251</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.48188</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.77278</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.5880299999999999</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.56152</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.6277200000000001</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46919</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.47871</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.55889</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.43106</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5930700000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.6686</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.81038</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.73203</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.64738</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.68947</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34338</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.33913</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.34409</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35079</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.30585</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33403</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.30706</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33399</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.32153</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.09791</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.36637</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.36781</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.35599</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.39724</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.36681</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.36905</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.34264</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.24171</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.30931</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.30215</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34115</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.33224</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.19452</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.24783</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.03217</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.17031</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.30679</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.27683</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.03005</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>-0.01864</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.17312</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.19221</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03446</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.05509</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.3072</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.2746</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.23366</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.25077</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34968</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34917</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.36828</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.37427</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.3697</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.42974</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.40628</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36987</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.37684</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37985</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.3844</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.42315</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.43129</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.5548200000000001</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.44142</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.45046</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.47686</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.46519</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.47446</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.43668</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42488</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.41846</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.3804</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43539</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3851</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.37998</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36418</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3862</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.07221</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.42604</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.42646</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.48417</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43632</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.39237</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.40068</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.39006</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.38651</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38326</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.3847</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.38388</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3791</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37529</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.37389</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.36703</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3754</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.36867</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.37125</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.37473</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3765</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34883</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>-0.03422</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35132</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.26653</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30355</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.28456</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.14992</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29479</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.28938</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29279</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.23673</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.11371</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29367</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.27784</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.42607</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.27762</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31263</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35276</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35106</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.43087</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.43313</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.4367200000000001</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.4362</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.45009</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.37048</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.3771</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.39634</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.39423</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.3707</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38138</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.42234</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.39429</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.38695</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.45168</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38673</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.42294</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40994</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.41199</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.3693</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36935</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37069</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3487</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.44917</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.40134</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37296</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.38751</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.38653</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.38604</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.38211</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.38376</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37542</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.37443</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.37567</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.37262</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.37252</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.36977</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36811</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.3641</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.36229</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.36341</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31919</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17679</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.28914</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14643</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19963</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.23714</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.04732</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.04755</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0352</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17732</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>-0.04893</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15787</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.24205</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.04973</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20206</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.04679999999999999</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26433</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.27589</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32397</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36527</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.47472</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.39922</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39581</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.40383</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.37787</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.46132</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.40973</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.42942</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.45961</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.41517</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.3988</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.44061</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.42283</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.44299</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.50129</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41072</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.40698</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38423</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.39024</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.39454</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.39442</v>
       </c>
     </row>
   </sheetData>
